--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_274_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_274_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5533</v>
+        <v>6.9229</v>
       </c>
       <c r="E2" t="n">
         <v>5.2605</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2927</v>
+        <v>1.6624</v>
       </c>
       <c r="G2" t="n">
         <v>5.961</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4257</v>
+        <v>-0.056</v>
       </c>
       <c r="T2" t="n">
         <v>-0.5895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1639</v>
+        <v>0.5335</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4024</v>
+        <v>4.5443</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3567</v>
+        <v>2.4314</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0457</v>
+        <v>2.1129</v>
       </c>
       <c r="G3" t="n">
         <v>2.363</v>
@@ -688,13 +688,13 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0482</v>
+        <v>-0.9063</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7389</v>
+        <v>-0.6642</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3093</v>
+        <v>-0.242</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7535</v>
+        <v>3.3705</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7336</v>
+        <v>2.0701</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0199</v>
+        <v>1.3004</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1182</v>
+        <v>2.8068</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1621</v>
+        <v>0.5114</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0439</v>
+        <v>2.2953</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1115</v>
+        <v>2.4316</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8907</v>
+        <v>0.5546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2208</v>
+        <v>1.8771</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9933</v>
+        <v>0.3752</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2714</v>
+        <v>-0.0431</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2647</v>
+        <v>0.4183</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1224</v>
+        <v>0.172</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1968</v>
+        <v>-0.3615</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9256</v>
+        <v>0.5335</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4254</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1682</v>
+        <v>3.2317</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8342</v>
+        <v>1.3798</v>
       </c>
       <c r="F5" t="n">
-        <v>1.334</v>
+        <v>1.8519</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8068</v>
+        <v>0.1182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5114</v>
+        <v>1.1621</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2953</v>
+        <v>-1.0439</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4316</v>
+        <v>1.1115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5546</v>
+        <v>0.8907</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8771</v>
+        <v>0.2208</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3752</v>
+        <v>-0.9933</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0431</v>
+        <v>0.2714</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4183</v>
+        <v>-1.2647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0303</v>
+        <v>0.6005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5975</v>
+        <v>-0.1571</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5671</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>0.4254</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7905</v>
+        <v>2.2019</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5249</v>
+        <v>1.8355</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2656</v>
+        <v>0.3664</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4958</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2498</v>
+        <v>-0.8384</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>-0.3536</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5856</v>
+        <v>-0.4848</v>
       </c>
       <c r="V6" t="n">
         <v>2.6805</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7742</v>
+        <v>1.8824</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4999</v>
+        <v>0.5746</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2743</v>
+        <v>1.3079</v>
       </c>
       <c r="G7" t="n">
         <v>0.5173</v>
@@ -1000,13 +1000,13 @@
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0627</v>
+        <v>-0.9544</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>-0.5149</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4731</v>
+        <v>-0.4395</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7381</v>
+        <v>1.6522</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3569</v>
+        <v>-0.2075</v>
       </c>
       <c r="F8" t="n">
-        <v>2.095</v>
+        <v>1.8597</v>
       </c>
       <c r="G8" t="n">
         <v>1.4548</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0514</v>
+        <v>-0.0345</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0376</v>
+        <v>-0.8883</v>
       </c>
       <c r="U8" t="n">
-        <v>1.089</v>
+        <v>0.8538</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1054</v>
+        <v>-0.1577</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5564</v>
+        <v>-0.4071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.451</v>
+        <v>0.2494</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7875</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1581</v>
+        <v>-0.2104</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>-0.5895</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5808</v>
+        <v>0.3791</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3173</v>
+        <v>-0.9925</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8871</v>
+        <v>-0.663</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4303</v>
+        <v>-0.3295</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5857</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4818</v>
+        <v>-1.1569</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8883</v>
+        <v>-0.6642</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5935</v>
+        <v>-0.4927</v>
       </c>
       <c r="V10" t="n">
         <v>1.214</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4359</v>
+        <v>-2.5577</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9827</v>
+        <v>-3.303</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.7452</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4278</v>
+        <v>-3.6234</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3504</v>
+        <v>-1.3314</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0774</v>
+        <v>-2.292</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2341</v>
+        <v>-2.9338</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0504</v>
+        <v>-1.4348</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2845</v>
+        <v>-1.4991</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1937</v>
+        <v>-0.6895</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4008</v>
+        <v>0.1034</v>
       </c>
       <c r="O11" t="n">
         <v>-0.7929</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6361</v>
+        <v>-0.9318</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1766</v>
+        <v>-0.279</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8127</v>
+        <v>-0.6528</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2525</v>
+        <v>0.1418</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2525</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1372</v>
+        <v>-2.842</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6136</v>
+        <v>-3.1872</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4764</v>
+        <v>0.3452</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6234</v>
+        <v>-1.4278</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3314</v>
+        <v>-0.3504</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.292</v>
+        <v>-1.0774</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9338</v>
+        <v>-0.2341</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4348</v>
+        <v>0.0504</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4991</v>
+        <v>-0.2845</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6895</v>
+        <v>-1.1937</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1034</v>
+        <v>-0.4008</v>
       </c>
       <c r="O12" t="n">
         <v>-0.7929</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5112</v>
+        <v>0.23</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5895</v>
+        <v>-0.3811</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9216</v>
+        <v>0.6111</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5316</v>
+        <v>-3.483</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3996</v>
+        <v>-3.2503</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.132</v>
+        <v>-0.2328</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7426</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3071</v>
+        <v>-0.2585</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.3734</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2157</v>
+        <v>0.1149</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.6528</v>
+        <v>13.773</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4135</v>
+        <v>2.533799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2392</v>
+        <v>11.2391</v>
       </c>
       <c r="G14" t="n">
         <v>3.5583</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6661</v>
+        <v>5.666100000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-2.1081</v>
@@ -1531,7 +1531,7 @@
         <v>-8.110799999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08550000000000002</v>
+        <v>0.08550000000000008</v>
       </c>
       <c r="O14" t="n">
         <v>-8.196400000000001</v>
@@ -1540,16 +1540,16 @@
         <v>9.278099999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.278300000000002</v>
+        <v>-9.2783</v>
       </c>
       <c r="R14" t="n">
         <v>18.5563</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.465</v>
+        <v>-4.3447</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.9365</v>
+        <v>-5.816300000000001</v>
       </c>
       <c r="U14" t="n">
         <v>1.4717</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2849</v>
+        <v>5.0706</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4477</v>
+        <v>4.6836</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1628</v>
+        <v>0.387</v>
       </c>
       <c r="G15" t="n">
         <v>5.9527</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6884</v>
+        <v>0.0973</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7389</v>
+        <v>-0.503</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0505</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2836</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2714</v>
+        <v>3.6215</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2331</v>
+        <v>0.9972</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0383</v>
+        <v>2.6243</v>
       </c>
       <c r="G16" t="n">
         <v>2.5862</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2883</v>
+        <v>1.6384</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6765</v>
+        <v>0.4406</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6118</v>
+        <v>1.1978</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0353</v>
+        <v>1.8159</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6132</v>
+        <v>1.2593</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4221</v>
+        <v>0.5566</v>
       </c>
       <c r="G17" t="n">
         <v>1.2932</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6519</v>
+        <v>0.4325</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.239</v>
+        <v>0.3734</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5888</v>
+        <v>1.5045</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3298</v>
+        <v>0.4958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9187</v>
+        <v>1.0087</v>
       </c>
       <c r="G18" t="n">
         <v>2.1109</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2179</v>
+        <v>0.6978</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0455</v>
+        <v>-0.2199</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8276</v>
+        <v>0.9177</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.542</v>
+        <v>-0.3953</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6556</v>
+        <v>-1.4813</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1976</v>
+        <v>1.086</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4486</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9004</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6097</v>
+        <v>-0.2159</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2907</v>
+        <v>1.1791</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0533</v>
+        <v>-0.9851</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5466</v>
+        <v>-0.542</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5067</v>
+        <v>-0.4431</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8463</v>
+        <v>-0.7718</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1512</v>
+        <v>-0.8187</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9975</v>
+        <v>0.0469</v>
       </c>
       <c r="J20" t="n">
-        <v>0.491</v>
+        <v>-0.1607</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5412</v>
+        <v>-0.7863</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0502</v>
+        <v>0.6257</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3373</v>
+        <v>-0.6112</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.39</v>
+        <v>-0.0323</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9473</v>
+        <v>-0.5788</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2568</v>
+        <v>0.0187</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1221</v>
+        <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1347</v>
+        <v>0.168</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2432</v>
+        <v>-1.5524</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.542</v>
+        <v>-0.9005</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7012</v>
+        <v>-0.6519</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7718</v>
+        <v>-1.8463</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8187</v>
+        <v>0.1512</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0469</v>
+        <v>-1.9975</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1607</v>
+        <v>0.491</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7863</v>
+        <v>0.5412</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6257</v>
+        <v>-0.0502</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6112</v>
+        <v>-2.3373</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0323</v>
+        <v>-0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5788</v>
+        <v>-1.9473</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2394</v>
+        <v>0.7578</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.2317</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0901</v>
+        <v>0.9895</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7673</v>
+        <v>-1.5849</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1585</v>
+        <v>-1.5596</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6087</v>
+        <v>-0.0253</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9383</v>
+        <v>-3.3895</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3722</v>
+        <v>-2.6266</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.566</v>
+        <v>-0.7629</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2525</v>
+        <v>-1.7564</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3431</v>
+        <v>-2.2582</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0906</v>
+        <v>0.5018</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1908</v>
+        <v>-1.6331</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7153</v>
+        <v>-0.3684</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4755</v>
+        <v>-1.2647</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9391</v>
+        <v>0.6449</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9085</v>
+        <v>0.1968</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0306</v>
+        <v>0.4481</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8537</v>
+        <v>-2.3735</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5596</v>
+        <v>-1.6303</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2941</v>
+        <v>-0.7432</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3895</v>
+        <v>-1.9383</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6266</v>
+        <v>-0.3722</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7629</v>
+        <v>-1.566</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7564</v>
+        <v>0.2525</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2582</v>
+        <v>0.3431</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5018</v>
+        <v>-0.0906</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6331</v>
+        <v>-2.1908</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3684</v>
+        <v>-0.7153</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2647</v>
+        <v>-1.4755</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.376</v>
+        <v>1.3328</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1968</v>
+        <v>0.4367</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1792</v>
+        <v>0.8962</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2183</v>
+        <v>-3.9266</v>
       </c>
       <c r="E24" t="n">
         <v>-2.7255</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4928</v>
+        <v>-1.2011</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5687</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7398</v>
+        <v>-0.4481</v>
       </c>
       <c r="T24" t="n">
         <v>-0.6721</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0677</v>
+        <v>0.224</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3319</v>
+        <v>-4.1023</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.668</v>
+        <v>-2.6064</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6639</v>
+        <v>-1.4958</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8306</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0373</v>
+        <v>1.1923</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1202</v>
+        <v>-0.0587</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0829</v>
+        <v>1.2509</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1444</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.907400000000001</v>
+        <v>-8.172499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.3474</v>
+        <v>-7.2295</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.56</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-2.7074</v>
@@ -2482,13 +2482,13 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0249</v>
+        <v>-0.2899</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3528</v>
+        <v>0.2642</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5361</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-12.6527</v>
+        <v>-11.0801</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.239</v>
+        <v>-11.2392</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4135</v>
+        <v>0.1591999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.5582</v>
+        <v>-3.558200000000001</v>
       </c>
       <c r="H27" t="n">
         <v>-5.6661</v>
@@ -2533,10 +2533,10 @@
         <v>2.107700000000002</v>
       </c>
       <c r="J27" t="n">
-        <v>8.110600000000002</v>
+        <v>8.1106</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.08560000000000012</v>
+        <v>-0.08560000000000034</v>
       </c>
       <c r="L27" t="n">
         <v>8.196299999999999</v>
@@ -2551,7 +2551,7 @@
         <v>-6.0886</v>
       </c>
       <c r="P27" t="n">
-        <v>-9.278100000000002</v>
+        <v>-9.2781</v>
       </c>
       <c r="Q27" t="n">
         <v>-18.5563</v>
@@ -2560,13 +2560,13 @@
         <v>9.278499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>5.4648</v>
+        <v>7.0377</v>
       </c>
       <c r="T27" t="n">
         <v>-1.4717</v>
       </c>
       <c r="U27" t="n">
-        <v>6.936399999999999</v>
+        <v>8.509200000000002</v>
       </c>
       <c r="V27" t="n">
         <v>-5.281400000000001</v>
